--- a/public/plantilla-importacion-deinsa-crm.xlsx
+++ b/public/plantilla-importacion-deinsa-crm.xlsx
@@ -5,16 +5,15 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jnlop\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/234ef745b869879d/Documents/CRM_deinsa/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDBF2603-479A-47D5-B1F5-A85408D62F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{DDBF2603-479A-47D5-B1F5-A85408D62F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75504A09-20DA-496B-B28C-97FDA1DFB572}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="1" r:id="rId1"/>
-    <sheet name="Table 2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <r>
       <rPr>
@@ -168,184 +167,6 @@
         <family val="2"/>
       </rPr>
       <t>Respuesta</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Mexico</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Gubernamental</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Agroasemex</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Publica</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="4.5"/>
-        <color rgb="FF0462C1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://www.gob.mx/agroasemex</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Marco Antonio Martínez Estrada</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Gerencia de Riezgos B</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="4.5"/>
-        <color rgb="FF0462C1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">linkedin.com/in/marco-antonio-martínez-estrada-
-</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="4.5"/>
-        <color rgb="FF0462C1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>https://www.gob.mx/agroasemex</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <color rgb="FF0462C1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="4.5"/>
-        <color rgb="FF0462C1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>a19167246</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="4.5"/>
-        <color rgb="FF0462C1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>mmartinez@arosemex.gob.mx</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>8000993939   Ext. 4376</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Fernando Diaz García</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Gerencia de Recursos Humanos</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="4.5"/>
-        <color rgb="FF0462C1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>fdiaz@agroasemex.gob.mx</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>8000993939   Ext. 4101</t>
     </r>
   </si>
 </sst>
@@ -353,7 +174,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -366,10 +187,6 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="4.5"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
       <b/>
       <sz val="4.5"/>
       <color rgb="FFFFFFFF"/>
@@ -377,22 +194,10 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="4.5"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="4.5"/>
-      <color rgb="FF0462C1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="4.5"/>
-      <color rgb="FF0462C1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -408,7 +213,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -447,48 +252,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF6FAC46"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF6FAC46"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF6FAC46"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF6FAC46"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF6FAC46"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF6FAC46"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF6FAC46"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF6FAC46"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -507,32 +275,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -898,7 +642,9 @@
     <row r="8" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="9" spans="1:11" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="10" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="11" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G11" s="6"/>
+    </row>
     <row r="12" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="13" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="14" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -933,103 +679,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.33203125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="20.5" customWidth="1"/>
-    <col min="2" max="2" width="26.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="7.5" customWidth="1"/>
-    <col min="6" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="44.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="22.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="6.2" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="14"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="13"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A3:I3"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="G1" r:id="rId1" display="http://www.gob.mx/agroasemex" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="H1" r:id="rId2" display="mailto:mmartinez@arosemex.gob.mx" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
-    <hyperlink ref="G2" r:id="rId3" display="http://www.gob.mx/agroasemex" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
-    <hyperlink ref="H2" r:id="rId4" display="mailto:fdiaz@agroasemex.gob.mx" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/public/plantilla-importacion-deinsa-crm.xlsx
+++ b/public/plantilla-importacion-deinsa-crm.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/234ef745b869879d/Documents/CRM_deinsa/public/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jnlop\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{DDBF2603-479A-47D5-B1F5-A85408D62F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75504A09-20DA-496B-B28C-97FDA1DFB572}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71AF839F-1F90-49D3-90CD-C2D6643AB6A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Table 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Negociaciones" sheetId="4" r:id="rId1"/>
+    <sheet name="Alianzas" sheetId="5" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -36,12 +37,111 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="13">
+  <si>
+    <t>Respuesta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">columna </t>
+  </si>
+  <si>
+    <t>Cargo</t>
+  </si>
   <si>
     <r>
       <rPr>
         <b/>
-        <sz val="4.5"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Industria</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Pais</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Sector</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Sitio Web</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>URL LinkedIn</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Correo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Numero</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Empresa</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -49,132 +149,12 @@
       <t>Nombre</t>
     </r>
   </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="4.5"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Cargo</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="4.5"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Empresa</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="4.5"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Industria</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="4.5"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Pais</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="4.5"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Sector</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="4.5"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Sitio Web</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="4.5"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>URL LinkedIn</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="4.5"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Correo</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="4.5"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Numero</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="4.5"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Respuesta</t>
-    </r>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -182,20 +162,41 @@
       <charset val="204"/>
     </font>
     <font>
-      <b/>
-      <sz val="4.5"/>
-      <name val="Calibri"/>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Times New Roman"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
-      <sz val="4.5"/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -253,33 +254,56 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -581,101 +605,139 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.33203125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="20.5" customWidth="1"/>
-    <col min="2" max="2" width="26.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="7.5" customWidth="1"/>
-    <col min="6" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="17.5" customWidth="1"/>
-    <col min="8" max="8" width="27.1640625" customWidth="1"/>
-    <col min="9" max="9" width="16" customWidth="1"/>
-    <col min="10" max="10" width="15.1640625" customWidth="1"/>
-    <col min="11" max="11" width="7.83203125" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DF3E2DB-C832-40E2-9595-9200EC7F3110}">
+  <dimension ref="A1:L4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:12" ht="30" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="L1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H3" s="2"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4008D83-FD6C-45DC-8F8F-6062572289A5}">
+  <dimension ref="A1:L3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:12" ht="30" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="C1" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
-        <v>10</v>
+      <c r="K1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="3" spans="1:11" ht="9.6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="1:11" ht="8.1" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="1:11" ht="9.6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="6" spans="1:11" ht="9.1999999999999993" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="7" spans="1:11" ht="9.6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="8" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="9" spans="1:11" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="10" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G11" s="6"/>
+    <row r="2" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
     </row>
-    <row r="12" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="13" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="15" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="16" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="17" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="18" ht="10.7" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" ht="10.35" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="20" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" ht="9.6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" ht="9.6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" ht="14.1" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" ht="8.85" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" ht="10.7" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H3" s="2"/>
+      <c r="I3" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
